--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574154576</v>
+        <v>46157.93116566881</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116566881</v>
+        <v>46157.93182892653</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93182892653</v>
+        <v>46157.93405423758</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405423758</v>
+        <v>46157.93723519606</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723519606</v>
+        <v>46158.28221314485</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221314485</v>
+        <v>46158.29701499125</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701499125</v>
+        <v>46158.29821022435</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821022435</v>
+        <v>46158.33392362873</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392362873</v>
+        <v>46158.36862109158</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862109158</v>
+        <v>46158.37292966196</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
